--- a/data/reviews.xlsx
+++ b/data/reviews.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pugin\Desktop\мои\Виктория\Github\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596B3DF3-D006-47AD-9DBC-E555B6D7FC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="L1" sheetId="1" r:id="rId5"/>
+    <sheet name="L1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'L1'!$F$1:$F$999</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'L1'!$F$1:$F$999</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="309">
   <si>
     <t>buyer_name</t>
   </si>
@@ -940,59 +950,30 @@
   </si>
   <si>
     <t>04 декабря 2024, 20:01</t>
-  </si>
-  <si>
-    <t>Станислав</t>
-  </si>
-  <si>
-    <t>17 августа 2024, 22:17</t>
-  </si>
-  <si>
-    <t>05 апреля, 12:14</t>
-  </si>
-  <si>
-    <t>Все комментарии покупные не может быть все пятёрки если товар не соответствует качеству просто хлам какой-то продаёте мошенники</t>
-  </si>
-  <si>
-    <t>30 марта, 19:45</t>
-  </si>
-  <si>
-    <t>24 июня 2024, 20:55</t>
-  </si>
-  <si>
-    <t>брак</t>
-  </si>
-  <si>
-    <t>18 ноября 2024, 21:16</t>
-  </si>
-  <si>
-    <t>01 ноября, 03:11</t>
-  </si>
-  <si>
-    <t>02 февраля, 22:26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Consolas"/>
     </font>
@@ -1002,37 +983,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1040,7 +1027,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1230,35 +1217,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L999"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.78"/>
-    <col customWidth="1" min="2" max="2" width="17.89"/>
-    <col customWidth="1" min="3" max="3" width="14.78"/>
-    <col customWidth="1" min="4" max="4" width="20.0"/>
-    <col customWidth="1" min="5" max="6" width="16.78"/>
-    <col customWidth="1" min="7" max="7" width="13.56"/>
-    <col customWidth="1" min="8" max="8" width="69.56"/>
-    <col customWidth="1" min="9" max="9" width="17.67"/>
-    <col customWidth="1" min="10" max="10" width="16.0"/>
-    <col customWidth="1" min="11" max="11" width="18.22"/>
-    <col customWidth="1" min="12" max="12" width="180.78"/>
-    <col customWidth="1" min="13" max="27" width="6.78"/>
+    <col min="1" max="1" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="14.75" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="69.5" customWidth="1"/>
+    <col min="9" max="9" width="17.625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
+    <col min="12" max="12" width="180.75" customWidth="1"/>
+    <col min="13" max="27" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1267,16 +1254,16 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1292,9 +1279,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -1308,8 +1295,8 @@
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3">
-        <f t="shared" ref="F2:F133" si="1">IF(ISERR(FIND("2024", E2)),
+      <c r="F2" s="2">
+        <f t="shared" ref="F2:F133" ca="1" si="0">IF(ISERR(FIND("2024", E2)),
      DATE(YEAR(TODAY()),
           MATCH(MID(E2, FIND(" ", E2)+1, FIND(",", E2)-FIND(" ", E2)-1),
                   {"января","февраля","марта","апреля","мая","июня","июля","августа","сентября","октября","ноября","декабря"},0),
@@ -1320,8 +1307,8 @@
           --LEFT(E2, FIND(" ", E2)-1)))</f>
         <v>46039</v>
       </c>
-      <c r="G2" s="4">
-        <v>45674.0</v>
+      <c r="G2" s="3">
+        <v>45674</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>14</v>
@@ -1339,9 +1326,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -1355,12 +1342,12 @@
       <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="3">
-        <f t="shared" si="1"/>
+      <c r="F3" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46272</v>
       </c>
-      <c r="G3" s="4">
-        <v>45907.0</v>
+      <c r="G3" s="3">
+        <v>45907</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>16</v>
@@ -1378,9 +1365,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
@@ -1394,12 +1381,12 @@
       <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3">
-        <f t="shared" si="1"/>
+      <c r="F4" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46288</v>
       </c>
-      <c r="G4" s="4">
-        <v>45923.0</v>
+      <c r="G4" s="3">
+        <v>45923</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>24</v>
@@ -1417,9 +1404,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>26</v>
@@ -1433,12 +1420,12 @@
       <c r="E5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="3">
-        <f t="shared" si="1"/>
+      <c r="F5" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46295</v>
       </c>
-      <c r="G5" s="4">
-        <v>45930.0</v>
+      <c r="G5" s="3">
+        <v>45930</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>16</v>
@@ -1456,9 +1443,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -1472,12 +1459,12 @@
       <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="3">
-        <f t="shared" si="1"/>
+      <c r="F6" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45543</v>
       </c>
-      <c r="G6" s="4">
-        <v>45543.0</v>
+      <c r="G6" s="3">
+        <v>45543</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>16</v>
@@ -1495,9 +1482,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>31</v>
@@ -1511,12 +1498,12 @@
       <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="3">
-        <f t="shared" si="1"/>
+      <c r="F7" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46340</v>
       </c>
-      <c r="G7" s="4">
-        <v>45975.0</v>
+      <c r="G7" s="3">
+        <v>45975</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>34</v>
@@ -1534,9 +1521,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -1550,12 +1537,12 @@
       <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="3">
-        <f t="shared" si="1"/>
+      <c r="F8" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46141</v>
       </c>
-      <c r="G8" s="4">
-        <v>45776.0</v>
+      <c r="G8" s="3">
+        <v>45776</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>16</v>
@@ -1573,9 +1560,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -1589,12 +1576,12 @@
       <c r="E9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="3">
-        <f t="shared" si="1"/>
+      <c r="F9" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46352</v>
       </c>
-      <c r="G9" s="4">
-        <v>45987.0</v>
+      <c r="G9" s="3">
+        <v>45987</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>16</v>
@@ -1612,9 +1599,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
@@ -1628,12 +1615,12 @@
       <c r="E10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="3">
-        <f t="shared" si="1"/>
+      <c r="F10" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45599</v>
       </c>
-      <c r="G10" s="4">
-        <v>45599.0</v>
+      <c r="G10" s="3">
+        <v>45599</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>41</v>
@@ -1651,9 +1638,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
@@ -1667,12 +1654,12 @@
       <c r="E11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="3">
-        <f t="shared" si="1"/>
+      <c r="F11" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46127</v>
       </c>
-      <c r="G11" s="4">
-        <v>45762.0</v>
+      <c r="G11" s="3">
+        <v>45762</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>45</v>
@@ -1690,9 +1677,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>46</v>
@@ -1706,12 +1693,12 @@
       <c r="E12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="3">
-        <f t="shared" si="1"/>
+      <c r="F12" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46235</v>
       </c>
-      <c r="G12" s="4">
-        <v>45870.0</v>
+      <c r="G12" s="3">
+        <v>45870</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>16</v>
@@ -1729,9 +1716,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -1745,12 +1732,12 @@
       <c r="E13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="3">
-        <f t="shared" si="1"/>
+      <c r="F13" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46125</v>
       </c>
-      <c r="G13" s="4">
-        <v>45760.0</v>
+      <c r="G13" s="3">
+        <v>45760</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>51</v>
@@ -1768,9 +1755,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>52</v>
@@ -1784,12 +1771,12 @@
       <c r="E14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="3">
-        <f t="shared" si="1"/>
+      <c r="F14" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46059</v>
       </c>
-      <c r="G14" s="4">
-        <v>45694.0</v>
+      <c r="G14" s="3">
+        <v>45694</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>55</v>
@@ -1807,9 +1794,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -1823,12 +1810,12 @@
       <c r="E15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="3">
-        <f t="shared" si="1"/>
+      <c r="F15" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46125</v>
       </c>
-      <c r="G15" s="4">
-        <v>45760.0</v>
+      <c r="G15" s="3">
+        <v>45760</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>57</v>
@@ -1846,9 +1833,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -1862,12 +1849,12 @@
       <c r="E16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="3">
-        <f t="shared" si="1"/>
+      <c r="F16" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45385</v>
       </c>
-      <c r="G16" s="4">
-        <v>45385.0</v>
+      <c r="G16" s="3">
+        <v>45385</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>16</v>
@@ -1885,9 +1872,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
@@ -1901,12 +1888,12 @@
       <c r="E17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="3">
-        <f t="shared" si="1"/>
+      <c r="F17" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46051</v>
       </c>
-      <c r="G17" s="4">
-        <v>45686.0</v>
+      <c r="G17" s="3">
+        <v>45686</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>61</v>
@@ -1924,9 +1911,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>62</v>
@@ -1940,12 +1927,12 @@
       <c r="E18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="3">
-        <f t="shared" si="1"/>
+      <c r="F18" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46124</v>
       </c>
-      <c r="G18" s="4">
-        <v>45759.0</v>
+      <c r="G18" s="3">
+        <v>45759</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>65</v>
@@ -1963,9 +1950,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>66</v>
@@ -1979,12 +1966,12 @@
       <c r="E19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="3">
-        <f t="shared" si="1"/>
+      <c r="F19" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46139</v>
       </c>
-      <c r="G19" s="4">
-        <v>45774.0</v>
+      <c r="G19" s="3">
+        <v>45774</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>68</v>
@@ -2002,9 +1989,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>69</v>
@@ -2018,12 +2005,12 @@
       <c r="E20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="3">
-        <f t="shared" si="1"/>
+      <c r="F20" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45537</v>
       </c>
-      <c r="G20" s="4">
-        <v>45537.0</v>
+      <c r="G20" s="3">
+        <v>45537</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>16</v>
@@ -2041,9 +2028,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>72</v>
@@ -2057,12 +2044,12 @@
       <c r="E21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="3">
-        <f t="shared" si="1"/>
+      <c r="F21" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45597</v>
       </c>
-      <c r="G21" s="4">
-        <v>45597.0</v>
+      <c r="G21" s="3">
+        <v>45597</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>16</v>
@@ -2080,9 +2067,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
@@ -2096,12 +2083,12 @@
       <c r="E22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="3">
-        <f t="shared" si="1"/>
+      <c r="F22" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46325</v>
       </c>
-      <c r="G22" s="4">
-        <v>45960.0</v>
+      <c r="G22" s="3">
+        <v>45960</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>76</v>
@@ -2119,9 +2106,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>77</v>
@@ -2135,12 +2122,12 @@
       <c r="E23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="3">
-        <f t="shared" si="1"/>
+      <c r="F23" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46198</v>
       </c>
-      <c r="G23" s="4">
-        <v>45833.0</v>
+      <c r="G23" s="3">
+        <v>45833</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>16</v>
@@ -2158,9 +2145,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
@@ -2174,12 +2161,12 @@
       <c r="E24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="3">
-        <f t="shared" si="1"/>
+      <c r="F24" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46163</v>
       </c>
-      <c r="G24" s="4">
-        <v>45798.0</v>
+      <c r="G24" s="3">
+        <v>45798</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>81</v>
@@ -2197,9 +2184,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>82</v>
@@ -2213,12 +2200,12 @@
       <c r="E25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="3">
-        <f t="shared" si="1"/>
+      <c r="F25" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45577</v>
       </c>
-      <c r="G25" s="4">
-        <v>45577.0</v>
+      <c r="G25" s="3">
+        <v>45577</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>16</v>
@@ -2236,9 +2223,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>85</v>
@@ -2252,12 +2239,12 @@
       <c r="E26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="3">
-        <f t="shared" si="1"/>
+      <c r="F26" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45478</v>
       </c>
-      <c r="G26" s="4">
-        <v>45478.0</v>
+      <c r="G26" s="3">
+        <v>45478</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>16</v>
@@ -2275,9 +2262,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>88</v>
@@ -2291,12 +2278,12 @@
       <c r="E27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="3">
-        <f t="shared" si="1"/>
+      <c r="F27" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45552</v>
       </c>
-      <c r="G27" s="4">
-        <v>45552.0</v>
+      <c r="G27" s="3">
+        <v>45552</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>16</v>
@@ -2314,9 +2301,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
@@ -2330,12 +2317,12 @@
       <c r="E28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="3">
-        <f t="shared" si="1"/>
+      <c r="F28" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45540</v>
       </c>
-      <c r="G28" s="4">
-        <v>45540.0</v>
+      <c r="G28" s="3">
+        <v>45540</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>16</v>
@@ -2353,9 +2340,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>93</v>
@@ -2369,12 +2356,12 @@
       <c r="E29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="3">
-        <f t="shared" si="1"/>
+      <c r="F29" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46339</v>
       </c>
-      <c r="G29" s="4">
-        <v>45974.0</v>
+      <c r="G29" s="3">
+        <v>45974</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>16</v>
@@ -2392,9 +2379,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>96</v>
@@ -2408,12 +2395,12 @@
       <c r="E30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="3">
-        <f t="shared" si="1"/>
+      <c r="F30" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46080</v>
       </c>
-      <c r="G30" s="4">
-        <v>45715.0</v>
+      <c r="G30" s="3">
+        <v>45715</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>98</v>
@@ -2431,9 +2418,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -2447,12 +2434,12 @@
       <c r="E31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="3">
-        <f t="shared" si="1"/>
+      <c r="F31" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46160</v>
       </c>
-      <c r="G31" s="4">
-        <v>45795.0</v>
+      <c r="G31" s="3">
+        <v>45795</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>101</v>
@@ -2470,9 +2457,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>52</v>
@@ -2486,12 +2473,12 @@
       <c r="E32" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F32" s="3">
-        <f t="shared" si="1"/>
+      <c r="F32" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46339</v>
       </c>
-      <c r="G32" s="4">
-        <v>45974.0</v>
+      <c r="G32" s="3">
+        <v>45974</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>16</v>
@@ -2509,9 +2496,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>52</v>
@@ -2525,12 +2512,12 @@
       <c r="E33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="3">
-        <f t="shared" si="1"/>
+      <c r="F33" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46274</v>
       </c>
-      <c r="G33" s="4">
-        <v>45909.0</v>
+      <c r="G33" s="3">
+        <v>45909</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>16</v>
@@ -2548,9 +2535,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>105</v>
@@ -2564,12 +2551,12 @@
       <c r="E34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F34" s="3">
-        <f t="shared" si="1"/>
+      <c r="F34" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46122</v>
       </c>
-      <c r="G34" s="4">
-        <v>45757.0</v>
+      <c r="G34" s="3">
+        <v>45757</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>16</v>
@@ -2587,9 +2574,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>108</v>
@@ -2603,12 +2590,12 @@
       <c r="E35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F35" s="3">
-        <f t="shared" si="1"/>
+      <c r="F35" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46116</v>
       </c>
-      <c r="G35" s="4">
-        <v>45751.0</v>
+      <c r="G35" s="3">
+        <v>45751</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>110</v>
@@ -2626,9 +2613,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
@@ -2642,12 +2629,12 @@
       <c r="E36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F36" s="3">
-        <f t="shared" si="1"/>
+      <c r="F36" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46316</v>
       </c>
-      <c r="G36" s="4">
-        <v>45951.0</v>
+      <c r="G36" s="3">
+        <v>45951</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>113</v>
@@ -2665,9 +2652,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -2681,12 +2668,12 @@
       <c r="E37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="3">
-        <f t="shared" si="1"/>
+      <c r="F37" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46080</v>
       </c>
-      <c r="G37" s="4">
-        <v>45715.0</v>
+      <c r="G37" s="3">
+        <v>45715</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>115</v>
@@ -2704,9 +2691,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>116</v>
@@ -2720,12 +2707,12 @@
       <c r="E38" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F38" s="3">
-        <f t="shared" si="1"/>
+      <c r="F38" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46140</v>
       </c>
-      <c r="G38" s="4">
-        <v>45775.0</v>
+      <c r="G38" s="3">
+        <v>45775</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>118</v>
@@ -2743,9 +2730,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>119</v>
@@ -2759,12 +2746,12 @@
       <c r="E39" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F39" s="3">
-        <f t="shared" si="1"/>
+      <c r="F39" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45517</v>
       </c>
-      <c r="G39" s="4">
-        <v>45517.0</v>
+      <c r="G39" s="3">
+        <v>45517</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>16</v>
@@ -2782,9 +2769,9 @@
         <v>121</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -2798,12 +2785,12 @@
       <c r="E40" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F40" s="3">
-        <f t="shared" si="1"/>
+      <c r="F40" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46126</v>
       </c>
-      <c r="G40" s="4">
-        <v>45761.0</v>
+      <c r="G40" s="3">
+        <v>45761</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>125</v>
@@ -2821,9 +2808,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>126</v>
@@ -2837,12 +2824,12 @@
       <c r="E41" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F41" s="3">
-        <f t="shared" si="1"/>
+      <c r="F41" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46349</v>
       </c>
-      <c r="G41" s="4">
-        <v>45984.0</v>
+      <c r="G41" s="3">
+        <v>45984</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>128</v>
@@ -2860,9 +2847,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>129</v>
@@ -2876,12 +2863,12 @@
       <c r="E42" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F42" s="3">
-        <f t="shared" si="1"/>
+      <c r="F42" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46309</v>
       </c>
-      <c r="G42" s="4">
-        <v>45944.0</v>
+      <c r="G42" s="3">
+        <v>45944</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>131</v>
@@ -2899,9 +2886,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>62</v>
@@ -2915,12 +2902,12 @@
       <c r="E43" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="3">
-        <f t="shared" si="1"/>
+      <c r="F43" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46163</v>
       </c>
-      <c r="G43" s="4">
-        <v>45798.0</v>
+      <c r="G43" s="3">
+        <v>45798</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>81</v>
@@ -2938,9 +2925,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>132</v>
@@ -2954,12 +2941,12 @@
       <c r="E44" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F44" s="3">
-        <f t="shared" si="1"/>
+      <c r="F44" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46187</v>
       </c>
-      <c r="G44" s="4">
-        <v>45822.0</v>
+      <c r="G44" s="3">
+        <v>45822</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>134</v>
@@ -2977,9 +2964,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>10</v>
@@ -2993,12 +2980,12 @@
       <c r="E45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F45" s="3">
-        <f t="shared" si="1"/>
+      <c r="F45" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46065</v>
       </c>
-      <c r="G45" s="4">
-        <v>45700.0</v>
+      <c r="G45" s="3">
+        <v>45700</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>136</v>
@@ -3016,9 +3003,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>129</v>
@@ -3032,12 +3019,12 @@
       <c r="E46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F46" s="3">
-        <f t="shared" si="1"/>
+      <c r="F46" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46104</v>
       </c>
-      <c r="G46" s="4">
-        <v>45739.0</v>
+      <c r="G46" s="3">
+        <v>45739</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>16</v>
@@ -3055,9 +3042,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>139</v>
@@ -3071,12 +3058,12 @@
       <c r="E47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F47" s="3">
-        <f t="shared" si="1"/>
+      <c r="F47" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45409</v>
       </c>
-      <c r="G47" s="4">
-        <v>45409.0</v>
+      <c r="G47" s="3">
+        <v>45409</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>16</v>
@@ -3094,9 +3081,9 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>77</v>
@@ -3110,12 +3097,12 @@
       <c r="E48" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F48" s="3">
-        <f t="shared" si="1"/>
+      <c r="F48" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46142</v>
       </c>
-      <c r="G48" s="4">
-        <v>45777.0</v>
+      <c r="G48" s="3">
+        <v>45777</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>143</v>
@@ -3133,9 +3120,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>144</v>
@@ -3149,12 +3136,12 @@
       <c r="E49" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F49" s="3">
-        <f t="shared" si="1"/>
+      <c r="F49" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46354</v>
       </c>
-      <c r="G49" s="4">
-        <v>45989.0</v>
+      <c r="G49" s="3">
+        <v>45989</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>146</v>
@@ -3172,9 +3159,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>77</v>
@@ -3188,12 +3175,12 @@
       <c r="E50" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F50" s="3">
-        <f t="shared" si="1"/>
+      <c r="F50" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46336</v>
       </c>
-      <c r="G50" s="4">
-        <v>45971.0</v>
+      <c r="G50" s="3">
+        <v>45971</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>148</v>
@@ -3211,9 +3198,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>82</v>
@@ -3227,12 +3214,12 @@
       <c r="E51" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F51" s="3">
-        <f t="shared" si="1"/>
+      <c r="F51" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46367</v>
       </c>
-      <c r="G51" s="4">
-        <v>46002.0</v>
+      <c r="G51" s="3">
+        <v>46002</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>16</v>
@@ -3250,9 +3237,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>150</v>
@@ -3266,12 +3253,12 @@
       <c r="E52" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F52" s="3">
-        <f t="shared" si="1"/>
+      <c r="F52" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45453</v>
       </c>
-      <c r="G52" s="4">
-        <v>45453.0</v>
+      <c r="G52" s="3">
+        <v>45453</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>16</v>
@@ -3289,9 +3276,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>153</v>
@@ -3305,12 +3292,12 @@
       <c r="E53" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F53" s="3">
-        <f t="shared" si="1"/>
+      <c r="F53" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46329</v>
       </c>
-      <c r="G53" s="4">
-        <v>45964.0</v>
+      <c r="G53" s="3">
+        <v>45964</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>155</v>
@@ -3328,9 +3315,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>62</v>
@@ -3344,12 +3331,12 @@
       <c r="E54" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F54" s="3">
-        <f t="shared" si="1"/>
+      <c r="F54" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46291</v>
       </c>
-      <c r="G54" s="4">
-        <v>45926.0</v>
+      <c r="G54" s="3">
+        <v>45926</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>16</v>
@@ -3367,9 +3354,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>10</v>
@@ -3383,12 +3370,12 @@
       <c r="E55" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F55" s="3">
-        <f t="shared" si="1"/>
+      <c r="F55" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46104</v>
       </c>
-      <c r="G55" s="4">
-        <v>45739.0</v>
+      <c r="G55" s="3">
+        <v>45739</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>158</v>
@@ -3406,9 +3393,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>10</v>
@@ -3422,12 +3409,12 @@
       <c r="E56" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F56" s="3">
-        <f t="shared" si="1"/>
+      <c r="F56" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46214</v>
       </c>
-      <c r="G56" s="4">
-        <v>45849.0</v>
+      <c r="G56" s="3">
+        <v>45849</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>16</v>
@@ -3445,9 +3432,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>52</v>
@@ -3461,12 +3448,12 @@
       <c r="E57" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F57" s="3">
-        <f t="shared" si="1"/>
+      <c r="F57" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45435</v>
       </c>
-      <c r="G57" s="4">
-        <v>45435.0</v>
+      <c r="G57" s="3">
+        <v>45435</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>16</v>
@@ -3484,9 +3471,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>162</v>
@@ -3500,12 +3487,12 @@
       <c r="E58" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F58" s="3">
-        <f t="shared" si="1"/>
+      <c r="F58" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46347</v>
       </c>
-      <c r="G58" s="4">
-        <v>45982.0</v>
+      <c r="G58" s="3">
+        <v>45982</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>16</v>
@@ -3523,9 +3510,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>10</v>
@@ -3539,12 +3526,12 @@
       <c r="E59" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F59" s="3">
-        <f t="shared" si="1"/>
+      <c r="F59" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46224</v>
       </c>
-      <c r="G59" s="4">
-        <v>45859.0</v>
+      <c r="G59" s="3">
+        <v>45859</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>16</v>
@@ -3562,9 +3549,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>167</v>
@@ -3578,12 +3565,12 @@
       <c r="E60" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F60" s="3">
-        <f t="shared" si="1"/>
+      <c r="F60" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45440</v>
       </c>
-      <c r="G60" s="4">
-        <v>45440.0</v>
+      <c r="G60" s="3">
+        <v>45440</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>16</v>
@@ -3601,9 +3588,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>167</v>
@@ -3617,12 +3604,12 @@
       <c r="E61" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F61" s="3">
-        <f t="shared" si="1"/>
+      <c r="F61" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46326</v>
       </c>
-      <c r="G61" s="4">
-        <v>45961.0</v>
+      <c r="G61" s="3">
+        <v>45961</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>16</v>
@@ -3640,9 +3627,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>172</v>
@@ -3656,12 +3643,12 @@
       <c r="E62" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F62" s="3">
-        <f t="shared" si="1"/>
+      <c r="F62" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46289</v>
       </c>
-      <c r="G62" s="4">
-        <v>45924.0</v>
+      <c r="G62" s="3">
+        <v>45924</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>16</v>
@@ -3679,9 +3666,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>172</v>
@@ -3695,12 +3682,12 @@
       <c r="E63" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F63" s="3">
-        <f t="shared" si="1"/>
+      <c r="F63" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46335</v>
       </c>
-      <c r="G63" s="4">
-        <v>45970.0</v>
+      <c r="G63" s="3">
+        <v>45970</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>16</v>
@@ -3718,9 +3705,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>175</v>
@@ -3734,12 +3721,12 @@
       <c r="E64" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F64" s="3">
-        <f t="shared" si="1"/>
+      <c r="F64" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46122</v>
       </c>
-      <c r="G64" s="4">
-        <v>45757.0</v>
+      <c r="G64" s="3">
+        <v>45757</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>177</v>
@@ -3757,9 +3744,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>10</v>
@@ -3773,12 +3760,12 @@
       <c r="E65" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F65" s="3">
-        <f t="shared" si="1"/>
+      <c r="F65" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45607</v>
       </c>
-      <c r="G65" s="4">
-        <v>45607.0</v>
+      <c r="G65" s="3">
+        <v>45607</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>179</v>
@@ -3796,9 +3783,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>35</v>
@@ -3812,12 +3799,12 @@
       <c r="E66" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F66" s="3">
-        <f t="shared" si="1"/>
+      <c r="F66" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46337</v>
       </c>
-      <c r="G66" s="4">
-        <v>45972.0</v>
+      <c r="G66" s="3">
+        <v>45972</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>181</v>
@@ -3835,9 +3822,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>108</v>
@@ -3851,12 +3838,12 @@
       <c r="E67" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="3">
-        <f t="shared" si="1"/>
+      <c r="F67" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46181</v>
       </c>
-      <c r="G67" s="4">
-        <v>45816.0</v>
+      <c r="G67" s="3">
+        <v>45816</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>183</v>
@@ -3874,9 +3861,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>172</v>
@@ -3890,12 +3877,12 @@
       <c r="E68" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F68" s="3">
-        <f t="shared" si="1"/>
+      <c r="F68" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46150</v>
       </c>
-      <c r="G68" s="4">
-        <v>45785.0</v>
+      <c r="G68" s="3">
+        <v>45785</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>16</v>
@@ -3913,9 +3900,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>10</v>
@@ -3929,12 +3916,12 @@
       <c r="E69" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F69" s="3">
-        <f t="shared" si="1"/>
+      <c r="F69" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46205</v>
       </c>
-      <c r="G69" s="4">
-        <v>45840.0</v>
+      <c r="G69" s="3">
+        <v>45840</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>187</v>
@@ -3952,9 +3939,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>188</v>
@@ -3968,12 +3955,12 @@
       <c r="E70" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F70" s="3">
-        <f t="shared" si="1"/>
+      <c r="F70" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46151</v>
       </c>
-      <c r="G70" s="4">
-        <v>45786.0</v>
+      <c r="G70" s="3">
+        <v>45786</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>190</v>
@@ -3991,9 +3978,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>191</v>
@@ -4007,12 +3994,12 @@
       <c r="E71" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F71" s="3">
-        <f t="shared" si="1"/>
+      <c r="F71" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45609</v>
       </c>
-      <c r="G71" s="4">
-        <v>45609.0</v>
+      <c r="G71" s="3">
+        <v>45609</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>16</v>
@@ -4030,9 +4017,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>193</v>
@@ -4046,12 +4033,12 @@
       <c r="E72" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F72" s="3">
-        <f t="shared" si="1"/>
+      <c r="F72" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46366</v>
       </c>
-      <c r="G72" s="4">
-        <v>46001.0</v>
+      <c r="G72" s="3">
+        <v>46001</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>16</v>
@@ -4069,9 +4056,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>196</v>
@@ -4085,12 +4072,12 @@
       <c r="E73" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F73" s="3">
-        <f t="shared" si="1"/>
+      <c r="F73" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45393</v>
       </c>
-      <c r="G73" s="4">
-        <v>45393.0</v>
+      <c r="G73" s="3">
+        <v>45393</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>16</v>
@@ -4108,9 +4095,9 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>77</v>
@@ -4124,12 +4111,12 @@
       <c r="E74" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F74" s="3">
-        <f t="shared" si="1"/>
+      <c r="F74" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45382</v>
       </c>
-      <c r="G74" s="4">
-        <v>45382.0</v>
+      <c r="G74" s="3">
+        <v>45382</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>16</v>
@@ -4147,9 +4134,9 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>10</v>
@@ -4163,12 +4150,12 @@
       <c r="E75" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F75" s="3">
-        <f t="shared" si="1"/>
+      <c r="F75" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46252</v>
       </c>
-      <c r="G75" s="4">
-        <v>45887.0</v>
+      <c r="G75" s="3">
+        <v>45887</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>16</v>
@@ -4186,9 +4173,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>62</v>
@@ -4202,12 +4189,12 @@
       <c r="E76" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F76" s="3">
-        <f t="shared" si="1"/>
+      <c r="F76" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46319</v>
       </c>
-      <c r="G76" s="4">
-        <v>45954.0</v>
+      <c r="G76" s="3">
+        <v>45954</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>16</v>
@@ -4225,9 +4212,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>10</v>
@@ -4241,12 +4228,12 @@
       <c r="E77" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F77" s="3">
-        <f t="shared" si="1"/>
+      <c r="F77" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45398</v>
       </c>
-      <c r="G77" s="4">
-        <v>45398.0</v>
+      <c r="G77" s="3">
+        <v>45398</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>16</v>
@@ -4264,9 +4251,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>62</v>
@@ -4280,12 +4267,12 @@
       <c r="E78" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F78" s="3">
-        <f t="shared" si="1"/>
+      <c r="F78" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46244</v>
       </c>
-      <c r="G78" s="4">
-        <v>45879.0</v>
+      <c r="G78" s="3">
+        <v>45879</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>16</v>
@@ -4303,9 +4290,9 @@
         <v>206</v>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>207</v>
@@ -4319,12 +4306,12 @@
       <c r="E79" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F79" s="3">
-        <f t="shared" si="1"/>
+      <c r="F79" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46350</v>
       </c>
-      <c r="G79" s="4">
-        <v>45985.0</v>
+      <c r="G79" s="3">
+        <v>45985</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>16</v>
@@ -4342,9 +4329,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>77</v>
@@ -4358,12 +4345,12 @@
       <c r="E80" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F80" s="3">
-        <f t="shared" si="1"/>
+      <c r="F80" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46084</v>
       </c>
-      <c r="G80" s="4">
-        <v>45719.0</v>
+      <c r="G80" s="3">
+        <v>45719</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>211</v>
@@ -4381,9 +4368,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>213</v>
@@ -4397,12 +4384,12 @@
       <c r="E81" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F81" s="3">
-        <f t="shared" si="1"/>
+      <c r="F81" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46332</v>
       </c>
-      <c r="G81" s="4">
-        <v>45967.0</v>
+      <c r="G81" s="3">
+        <v>45967</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>16</v>
@@ -4420,9 +4407,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>129</v>
@@ -4436,12 +4423,12 @@
       <c r="E82" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F82" s="3">
-        <f t="shared" si="1"/>
+      <c r="F82" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46289</v>
       </c>
-      <c r="G82" s="4">
-        <v>45924.0</v>
+      <c r="G82" s="3">
+        <v>45924</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>16</v>
@@ -4459,9 +4446,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>172</v>
@@ -4475,12 +4462,12 @@
       <c r="E83" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F83" s="3">
-        <f t="shared" si="1"/>
+      <c r="F83" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46288</v>
       </c>
-      <c r="G83" s="4">
-        <v>45923.0</v>
+      <c r="G83" s="3">
+        <v>45923</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>16</v>
@@ -4498,9 +4485,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>217</v>
@@ -4514,12 +4501,12 @@
       <c r="E84" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F84" s="3">
-        <f t="shared" si="1"/>
+      <c r="F84" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45579</v>
       </c>
-      <c r="G84" s="4">
-        <v>45579.0</v>
+      <c r="G84" s="3">
+        <v>45579</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>16</v>
@@ -4537,9 +4524,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>220</v>
@@ -4553,12 +4540,12 @@
       <c r="E85" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F85" s="3">
-        <f t="shared" si="1"/>
+      <c r="F85" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45625</v>
       </c>
-      <c r="G85" s="4">
-        <v>45625.0</v>
+      <c r="G85" s="3">
+        <v>45625</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>222</v>
@@ -4576,9 +4563,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>223</v>
@@ -4592,12 +4579,12 @@
       <c r="E86" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F86" s="3">
-        <f t="shared" si="1"/>
+      <c r="F86" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46241</v>
       </c>
-      <c r="G86" s="4">
-        <v>45876.0</v>
+      <c r="G86" s="3">
+        <v>45876</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>16</v>
@@ -4615,9 +4602,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>172</v>
@@ -4631,12 +4618,12 @@
       <c r="E87" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F87" s="3">
-        <f t="shared" si="1"/>
+      <c r="F87" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46266</v>
       </c>
-      <c r="G87" s="4">
-        <v>45901.0</v>
+      <c r="G87" s="3">
+        <v>45901</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>16</v>
@@ -4654,9 +4641,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>226</v>
@@ -4670,12 +4657,12 @@
       <c r="E88" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F88" s="3">
-        <f t="shared" si="1"/>
+      <c r="F88" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45557</v>
       </c>
-      <c r="G88" s="4">
-        <v>45557.0</v>
+      <c r="G88" s="3">
+        <v>45557</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>16</v>
@@ -4693,9 +4680,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>10</v>
@@ -4709,12 +4696,12 @@
       <c r="E89" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F89" s="3">
-        <f t="shared" si="1"/>
+      <c r="F89" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46332</v>
       </c>
-      <c r="G89" s="4">
-        <v>45967.0</v>
+      <c r="G89" s="3">
+        <v>45967</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>229</v>
@@ -4732,9 +4719,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>129</v>
@@ -4748,12 +4735,12 @@
       <c r="E90" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F90" s="3">
-        <f t="shared" si="1"/>
+      <c r="F90" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46309</v>
       </c>
-      <c r="G90" s="4">
-        <v>45944.0</v>
+      <c r="G90" s="3">
+        <v>45944</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>230</v>
@@ -4771,9 +4758,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>231</v>
@@ -4787,12 +4774,12 @@
       <c r="E91" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F91" s="3">
-        <f t="shared" si="1"/>
+      <c r="F91" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46316</v>
       </c>
-      <c r="G91" s="4">
-        <v>45951.0</v>
+      <c r="G91" s="3">
+        <v>45951</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>16</v>
@@ -4810,9 +4797,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>233</v>
@@ -4826,12 +4813,12 @@
       <c r="E92" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F92" s="3">
-        <f t="shared" si="1"/>
+      <c r="F92" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46323</v>
       </c>
-      <c r="G92" s="4">
-        <v>45958.0</v>
+      <c r="G92" s="3">
+        <v>45958</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>16</v>
@@ -4849,9 +4836,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>235</v>
@@ -4865,12 +4852,12 @@
       <c r="E93" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F93" s="3">
-        <f t="shared" si="1"/>
+      <c r="F93" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45516</v>
       </c>
-      <c r="G93" s="4">
-        <v>45516.0</v>
+      <c r="G93" s="3">
+        <v>45516</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>16</v>
@@ -4888,9 +4875,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>172</v>
@@ -4904,12 +4891,12 @@
       <c r="E94" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F94" s="3">
-        <f t="shared" si="1"/>
+      <c r="F94" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45551</v>
       </c>
-      <c r="G94" s="4">
-        <v>45551.0</v>
+      <c r="G94" s="3">
+        <v>45551</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>16</v>
@@ -4927,9 +4914,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>10</v>
@@ -4943,12 +4930,12 @@
       <c r="E95" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F95" s="3">
-        <f t="shared" si="1"/>
+      <c r="F95" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46303</v>
       </c>
-      <c r="G95" s="4">
-        <v>45938.0</v>
+      <c r="G95" s="3">
+        <v>45938</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>16</v>
@@ -4966,9 +4953,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>62</v>
@@ -4982,12 +4969,12 @@
       <c r="E96" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F96" s="3">
-        <f t="shared" si="1"/>
+      <c r="F96" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46092</v>
       </c>
-      <c r="G96" s="4">
-        <v>45727.0</v>
+      <c r="G96" s="3">
+        <v>45727</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>242</v>
@@ -5005,9 +4992,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>35</v>
@@ -5021,12 +5008,12 @@
       <c r="E97" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F97" s="3">
-        <f t="shared" si="1"/>
+      <c r="F97" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45468</v>
       </c>
-      <c r="G97" s="4">
-        <v>45468.0</v>
+      <c r="G97" s="3">
+        <v>45468</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>16</v>
@@ -5044,9 +5031,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>245</v>
@@ -5060,12 +5047,12 @@
       <c r="E98" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F98" s="3">
-        <f t="shared" si="1"/>
+      <c r="F98" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45633</v>
       </c>
-      <c r="G98" s="4">
-        <v>45633.0</v>
+      <c r="G98" s="3">
+        <v>45633</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>247</v>
@@ -5083,9 +5070,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>248</v>
@@ -5099,12 +5086,12 @@
       <c r="E99" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F99" s="3">
-        <f t="shared" si="1"/>
+      <c r="F99" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46058</v>
       </c>
-      <c r="G99" s="4">
-        <v>45693.0</v>
+      <c r="G99" s="3">
+        <v>45693</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>250</v>
@@ -5122,9 +5109,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>251</v>
@@ -5138,12 +5125,12 @@
       <c r="E100" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F100" s="3">
-        <f t="shared" si="1"/>
+      <c r="F100" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45556</v>
       </c>
-      <c r="G100" s="4">
-        <v>45556.0</v>
+      <c r="G100" s="3">
+        <v>45556</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>16</v>
@@ -5161,9 +5148,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>254</v>
@@ -5177,12 +5164,12 @@
       <c r="E101" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F101" s="3">
-        <f t="shared" si="1"/>
+      <c r="F101" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45436</v>
       </c>
-      <c r="G101" s="4">
-        <v>45436.0</v>
+      <c r="G101" s="3">
+        <v>45436</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>16</v>
@@ -5200,9 +5187,9 @@
         <v>256</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>35</v>
@@ -5216,12 +5203,12 @@
       <c r="E102" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F102" s="3">
-        <f t="shared" si="1"/>
+      <c r="F102" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46143</v>
       </c>
-      <c r="G102" s="4">
-        <v>45778.0</v>
+      <c r="G102" s="3">
+        <v>45778</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>16</v>
@@ -5239,9 +5226,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>258</v>
@@ -5255,12 +5242,12 @@
       <c r="E103" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F103" s="3">
-        <f t="shared" si="1"/>
+      <c r="F103" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46270</v>
       </c>
-      <c r="G103" s="4">
-        <v>45905.0</v>
+      <c r="G103" s="3">
+        <v>45905</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>16</v>
@@ -5278,9 +5265,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>10</v>
@@ -5294,12 +5281,12 @@
       <c r="E104" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F104" s="3">
-        <f t="shared" si="1"/>
+      <c r="F104" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46074</v>
       </c>
-      <c r="G104" s="4">
-        <v>45709.0</v>
+      <c r="G104" s="3">
+        <v>45709</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>16</v>
@@ -5317,9 +5304,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>264</v>
@@ -5333,12 +5320,12 @@
       <c r="E105" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F105" s="3">
-        <f t="shared" si="1"/>
+      <c r="F105" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46369</v>
       </c>
-      <c r="G105" s="4">
-        <v>46004.0</v>
+      <c r="G105" s="3">
+        <v>46004</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>266</v>
@@ -5356,9 +5343,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>49</v>
@@ -5372,12 +5359,12 @@
       <c r="E106" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F106" s="3">
-        <f t="shared" si="1"/>
+      <c r="F106" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45516</v>
       </c>
-      <c r="G106" s="4">
-        <v>45516.0</v>
+      <c r="G106" s="3">
+        <v>45516</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>16</v>
@@ -5395,9 +5382,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>10</v>
@@ -5411,12 +5398,12 @@
       <c r="E107" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F107" s="3">
-        <f t="shared" si="1"/>
+      <c r="F107" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46066</v>
       </c>
-      <c r="G107" s="4">
-        <v>45701.0</v>
+      <c r="G107" s="3">
+        <v>45701</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>16</v>
@@ -5434,9 +5421,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>10</v>
@@ -5450,12 +5437,12 @@
       <c r="E108" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F108" s="3">
-        <f t="shared" si="1"/>
+      <c r="F108" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46353</v>
       </c>
-      <c r="G108" s="4">
-        <v>45988.0</v>
+      <c r="G108" s="3">
+        <v>45988</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>274</v>
@@ -5473,9 +5460,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>275</v>
@@ -5489,12 +5476,12 @@
       <c r="E109" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F109" s="3">
-        <f t="shared" si="1"/>
+      <c r="F109" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46157</v>
       </c>
-      <c r="G109" s="4">
-        <v>45792.0</v>
+      <c r="G109" s="3">
+        <v>45792</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>16</v>
@@ -5512,9 +5499,9 @@
         <v>277</v>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>278</v>
@@ -5528,12 +5515,12 @@
       <c r="E110" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F110" s="3">
-        <f t="shared" si="1"/>
+      <c r="F110" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45553</v>
       </c>
-      <c r="G110" s="4">
-        <v>45553.0</v>
+      <c r="G110" s="3">
+        <v>45553</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>16</v>
@@ -5551,9 +5538,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>82</v>
@@ -5567,12 +5554,12 @@
       <c r="E111" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F111" s="3">
-        <f t="shared" si="1"/>
+      <c r="F111" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46228</v>
       </c>
-      <c r="G111" s="4">
-        <v>45863.0</v>
+      <c r="G111" s="3">
+        <v>45863</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>16</v>
@@ -5590,9 +5577,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>281</v>
@@ -5606,12 +5593,12 @@
       <c r="E112" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F112" s="3">
-        <f t="shared" si="1"/>
+      <c r="F112" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46141</v>
       </c>
-      <c r="G112" s="4">
-        <v>45776.0</v>
+      <c r="G112" s="3">
+        <v>45776</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>16</v>
@@ -5629,9 +5616,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>283</v>
@@ -5645,12 +5632,12 @@
       <c r="E113" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F113" s="3">
-        <f t="shared" si="1"/>
+      <c r="F113" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46228</v>
       </c>
-      <c r="G113" s="4">
-        <v>45863.0</v>
+      <c r="G113" s="3">
+        <v>45863</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>285</v>
@@ -5668,9 +5655,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>286</v>
@@ -5684,12 +5671,12 @@
       <c r="E114" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F114" s="3">
-        <f t="shared" si="1"/>
+      <c r="F114" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45520</v>
       </c>
-      <c r="G114" s="4">
-        <v>45520.0</v>
+      <c r="G114" s="3">
+        <v>45520</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>16</v>
@@ -5707,9 +5694,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>10</v>
@@ -5723,12 +5710,12 @@
       <c r="E115" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F115" s="3">
-        <f t="shared" si="1"/>
+      <c r="F115" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46166</v>
       </c>
-      <c r="G115" s="4">
-        <v>45801.0</v>
+      <c r="G115" s="3">
+        <v>45801</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>16</v>
@@ -5746,9 +5733,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>10</v>
@@ -5762,12 +5749,12 @@
       <c r="E116" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F116" s="3">
-        <f t="shared" si="1"/>
+      <c r="F116" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46038</v>
       </c>
-      <c r="G116" s="4">
-        <v>45673.0</v>
+      <c r="G116" s="3">
+        <v>45673</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>16</v>
@@ -5785,9 +5772,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>82</v>
@@ -5801,12 +5788,12 @@
       <c r="E117" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F117" s="3">
-        <f t="shared" si="1"/>
+      <c r="F117" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46179</v>
       </c>
-      <c r="G117" s="4">
-        <v>45814.0</v>
+      <c r="G117" s="3">
+        <v>45814</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>291</v>
@@ -5824,9 +5811,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>82</v>
@@ -5840,12 +5827,12 @@
       <c r="E118" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F118" s="3">
-        <f t="shared" si="1"/>
+      <c r="F118" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46229</v>
       </c>
-      <c r="G118" s="4">
-        <v>45864.0</v>
+      <c r="G118" s="3">
+        <v>45864</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>16</v>
@@ -5863,9 +5850,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>294</v>
@@ -5879,12 +5866,12 @@
       <c r="E119" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F119" s="3">
-        <f t="shared" si="1"/>
+      <c r="F119" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46310</v>
       </c>
-      <c r="G119" s="4">
-        <v>45945.0</v>
+      <c r="G119" s="3">
+        <v>45945</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>16</v>
@@ -5902,9 +5889,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>10</v>
@@ -5918,12 +5905,12 @@
       <c r="E120" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F120" s="3">
-        <f t="shared" si="1"/>
+      <c r="F120" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46124</v>
       </c>
-      <c r="G120" s="4">
-        <v>45759.0</v>
+      <c r="G120" s="3">
+        <v>45759</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>298</v>
@@ -5941,9 +5928,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>52</v>
@@ -5957,12 +5944,12 @@
       <c r="E121" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F121" s="3">
-        <f t="shared" si="1"/>
+      <c r="F121" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46247</v>
       </c>
-      <c r="G121" s="4">
-        <v>45882.0</v>
+      <c r="G121" s="3">
+        <v>45882</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>16</v>
@@ -5980,9 +5967,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>10</v>
@@ -5996,12 +5983,12 @@
       <c r="E122" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F122" s="3">
-        <f t="shared" si="1"/>
+      <c r="F122" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46090</v>
       </c>
-      <c r="G122" s="4">
-        <v>45725.0</v>
+      <c r="G122" s="3">
+        <v>45725</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>16</v>
@@ -6019,9 +6006,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>10</v>
@@ -6035,12 +6022,12 @@
       <c r="E123" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F123" s="3">
-        <f t="shared" si="1"/>
+      <c r="F123" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45469</v>
       </c>
-      <c r="G123" s="4">
-        <v>45469.0</v>
+      <c r="G123" s="3">
+        <v>45469</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>16</v>
@@ -6058,9 +6045,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>52</v>
@@ -6074,12 +6061,12 @@
       <c r="E124" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F124" s="3">
-        <f t="shared" si="1"/>
+      <c r="F124" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46280</v>
       </c>
-      <c r="G124" s="4">
-        <v>45915.0</v>
+      <c r="G124" s="3">
+        <v>45915</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>16</v>
@@ -6097,9 +6084,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>10</v>
@@ -6113,12 +6100,12 @@
       <c r="E125" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F125" s="3">
-        <f t="shared" si="1"/>
+      <c r="F125" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>46066</v>
       </c>
-      <c r="G125" s="4">
-        <v>45701.0</v>
+      <c r="G125" s="3">
+        <v>45701</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>16</v>
@@ -6136,9 +6123,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>307</v>
@@ -6152,12 +6139,12 @@
       <c r="E126" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F126" s="3">
-        <f t="shared" si="1"/>
+      <c r="F126" s="2">
+        <f t="shared" ca="1" si="0"/>
         <v>45630</v>
       </c>
-      <c r="G126" s="4">
-        <v>45630.0</v>
+      <c r="G126" s="3">
+        <v>45630</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>16</v>
@@ -6175,1150 +6162,973 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F127" s="3">
-        <f t="shared" si="1"/>
-        <v>45521</v>
-      </c>
-      <c r="G127" s="4">
-        <v>45521.0</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F128" s="3">
-        <f t="shared" si="1"/>
-        <v>46117</v>
-      </c>
-      <c r="G128" s="4">
-        <v>45752.0</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F129" s="3">
-        <f t="shared" si="1"/>
-        <v>46111</v>
-      </c>
-      <c r="G129" s="4">
-        <v>45746.0</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L129" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F130" s="3">
-        <f t="shared" si="1"/>
-        <v>45467</v>
-      </c>
-      <c r="G130" s="4">
-        <v>45467.0</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L130" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F131" s="3">
-        <f t="shared" si="1"/>
-        <v>45614</v>
-      </c>
-      <c r="G131" s="4">
-        <v>45614.0</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F132" s="3">
-        <f t="shared" si="1"/>
-        <v>46327</v>
-      </c>
-      <c r="G132" s="4">
-        <v>45962.0</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L132" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F133" s="3">
-        <f t="shared" si="1"/>
-        <v>46055</v>
-      </c>
-      <c r="G133" s="4">
-        <v>45690.0</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="L127" s="1"/>
+    </row>
+    <row r="128" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+    </row>
+    <row r="129" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+    </row>
+    <row r="130" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+    </row>
+    <row r="131" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+    </row>
+    <row r="132" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+    </row>
+    <row r="133" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+    </row>
+    <row r="134" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="$F$1:$F$999"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="F1:F999" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>